--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484327_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484327_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4806</v>
+        <v>3.5829</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1399</v>
+        <v>-0.0224</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3407</v>
+        <v>3.6053</v>
       </c>
       <c r="G2" t="n">
         <v>2.895</v>
@@ -610,13 +610,13 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6089</v>
+        <v>0.7111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0442</v>
+        <v>-0.1181</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5646</v>
+        <v>0.8293</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2985</v>
+        <v>0.9104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1053</v>
+        <v>0.0441</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1932</v>
+        <v>0.8663</v>
       </c>
       <c r="G3" t="n">
         <v>1.5241</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7313</v>
+        <v>0.3432</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3548</v>
+        <v>-0.416</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0861</v>
+        <v>0.7592</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1522</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1643</v>
+        <v>0.4041</v>
       </c>
       <c r="E4" t="n">
-        <v>0.467</v>
+        <v>0.7903</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6313</v>
+        <v>-0.3862</v>
       </c>
       <c r="G4" t="n">
         <v>0.8247</v>
@@ -766,13 +766,13 @@
         <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6647</v>
+        <v>-0.0963</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5447</v>
+        <v>-0.2214</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.12</v>
+        <v>0.1251</v>
       </c>
       <c r="V4" t="n">
         <v>0.0664</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9912</v>
+        <v>-0.2556</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9287</v>
+        <v>-2.3021</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9376</v>
+        <v>2.0465</v>
       </c>
       <c r="G5" t="n">
         <v>0.9032</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8436</v>
+        <v>-0.108</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0619</v>
+        <v>-0.4352</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2183</v>
+        <v>0.3272</v>
       </c>
       <c r="V5" t="n">
         <v>0.1213</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2847</v>
+        <v>-0.6089</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9162</v>
+        <v>-2.483</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3685</v>
+        <v>1.8741</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.7502</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1348</v>
+        <v>-0.1696</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.079</v>
+        <v>-0.5805</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6741</v>
+        <v>-0.5947</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.0154</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>-0.5794</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.27</v>
+        <v>-0.1554</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1348</v>
+        <v>-0.1542</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4049</v>
+        <v>-0.0012</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3406</v>
+        <v>-0.1438</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2421</v>
+        <v>-0.7861</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0985</v>
+        <v>0.6423</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6757</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2905</v>
+        <v>-1.2303</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0284</v>
+        <v>-0.9162</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7379</v>
+        <v>-0.3141</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7502</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1696</v>
+        <v>0.1348</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5805</v>
+        <v>-1.079</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5947</v>
+        <v>-0.6741</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0154</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5794</v>
+        <v>-0.6741</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1554</v>
+        <v>-0.27</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1542</v>
+        <v>0.1348</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0012</v>
+        <v>-0.4049</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8254</v>
+        <v>-0.2861</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3315</v>
+        <v>-0.2421</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5061</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6757</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.457</v>
+        <v>-1.4626</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9614</v>
+        <v>-1.1031</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4957</v>
+        <v>-0.3595</v>
       </c>
       <c r="G8" t="n">
         <v>0.2471</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0688</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3853</v>
+        <v>0.2436</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4485</v>
+        <v>-0.3123</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6642</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.52</v>
+        <v>-2.0951</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6299</v>
+        <v>-3.2867</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1099</v>
+        <v>1.1916</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9002</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6664</v>
+        <v>-0.2415</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8335</v>
+        <v>-0.4903</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1672</v>
+        <v>0.2489</v>
       </c>
       <c r="V9" t="n">
         <v>2.4373</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3359</v>
+        <v>-4.1041</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9272</v>
+        <v>-4.9677</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5913</v>
+        <v>0.8636</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4764</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5585</v>
+        <v>-0.3267</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0851</v>
+        <v>-0.1257</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4733</v>
+        <v>-0.201</v>
       </c>
       <c r="V10" t="n">
         <v>0.0664</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0573</v>
+        <v>-4.9496</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3588</v>
+        <v>-4.2783</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6985</v>
+        <v>-0.6713</v>
       </c>
       <c r="G11" t="n">
         <v>-4.394</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3312</v>
+        <v>-0.2235</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2667</v>
+        <v>-0.1863</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0645</v>
+        <v>-0.0373</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.3218</v>
+        <v>-9.8088</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.0384</v>
+        <v>-18.5251</v>
       </c>
       <c r="F12" t="n">
-        <v>8.716600000000001</v>
+        <v>8.7163</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0708</v>
@@ -1390,13 +1390,13 @@
         <v>15.6274</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9534</v>
+        <v>-0.4404</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.2908</v>
+        <v>-2.777600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3375</v>
+        <v>2.3374</v>
       </c>
       <c r="V12" t="n">
         <v>0.6093</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0507</v>
+        <v>3.9805</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3481</v>
+        <v>2.5503</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7026</v>
+        <v>1.4302</v>
       </c>
       <c r="G13" t="n">
         <v>5.008</v>
@@ -1468,13 +1468,13 @@
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4566</v>
+        <v>0.3865</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4237</v>
+        <v>-0.2214</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8803</v>
+        <v>0.6079</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2186</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7138</v>
+        <v>2.9136</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3827</v>
+        <v>2.0394</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3311</v>
+        <v>0.8743</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6387</v>
+        <v>2.0667</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3694</v>
+        <v>0.9197</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2692</v>
+        <v>1.1471</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3194</v>
+        <v>3.0908</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1842</v>
+        <v>1.2689</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1352</v>
+        <v>1.8219</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3193</v>
+        <v>-1.0241</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1852</v>
+        <v>-0.3492</v>
       </c>
       <c r="O14" t="n">
-        <v>0.134</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1255</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.317</v>
+        <v>0.0069</v>
       </c>
       <c r="T14" t="n">
-        <v>0.212</v>
+        <v>-0.524</v>
       </c>
       <c r="U14" t="n">
-        <v>0.105</v>
+        <v>0.5309</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6024</v>
+        <v>2.7696</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8371</v>
+        <v>-0.0218</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7653</v>
+        <v>2.7914</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0667</v>
+        <v>0.6387</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9197</v>
+        <v>0.3694</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1471</v>
+        <v>0.2692</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0908</v>
+        <v>0.3194</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2689</v>
+        <v>0.1842</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8219</v>
+        <v>0.1352</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0241</v>
+        <v>0.3193</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3492</v>
+        <v>0.1852</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3043</v>
+        <v>0.3728</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.1924</v>
       </c>
       <c r="U15" t="n">
-        <v>0.422</v>
+        <v>0.5653</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4103</v>
+        <v>2.0374</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3482</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7585</v>
+        <v>1.3998</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8114</v>
+        <v>1.269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0565</v>
+        <v>0.2973</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7548</v>
+        <v>0.9718</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0474</v>
+        <v>0.6698</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2635</v>
+        <v>0.1023</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2161</v>
+        <v>0.5675</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8587</v>
+        <v>0.5992</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3201</v>
+        <v>0.1949</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5387</v>
+        <v>0.4043</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.5162</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9301</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5208</v>
+        <v>0.1823</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2805</v>
+        <v>-0.0322</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8013</v>
+        <v>0.2145</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8947</v>
+        <v>1.8098</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7387</v>
+        <v>-2.3482</v>
       </c>
       <c r="F17" t="n">
-        <v>1.156</v>
+        <v>4.1579</v>
       </c>
       <c r="G17" t="n">
-        <v>1.269</v>
+        <v>0.8114</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2973</v>
+        <v>0.0565</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9718</v>
+        <v>0.7548</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6698</v>
+        <v>-0.0474</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1023</v>
+        <v>-0.2635</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5675</v>
+        <v>0.2161</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5992</v>
+        <v>0.8587</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1949</v>
+        <v>0.3201</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4043</v>
+        <v>0.5387</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.5162</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0397</v>
+        <v>0.9203</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0689</v>
+        <v>-0.2805</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0292</v>
+        <v>1.2007</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1301</v>
+        <v>1.6421</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9912</v>
+        <v>-1.5867</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1213</v>
+        <v>3.2288</v>
       </c>
       <c r="G18" t="n">
         <v>0.8475</v>
@@ -1858,13 +1858,13 @@
         <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3621</v>
+        <v>0.15</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0894</v>
+        <v>-0.6849</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.8349</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3321</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4629</v>
+        <v>1.53</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1816</v>
+        <v>-2.0986</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6445</v>
+        <v>3.6286</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0747</v>
+        <v>-0.3745</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4792</v>
+        <v>-0.2671</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4045</v>
+        <v>-0.1074</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1.7031</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.3825</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.3206</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0747</v>
+        <v>1.3286</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4792</v>
+        <v>0.1154</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4045</v>
+        <v>1.2132</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0484</v>
+        <v>0.1231</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1816</v>
+        <v>-0.2468</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1331</v>
+        <v>0.3699</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3619</v>
+        <v>0.673</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8064</v>
+        <v>-0.0805</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1684</v>
+        <v>0.7534</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3745</v>
+        <v>-0.0747</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2671</v>
+        <v>-0.4792</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1074</v>
+        <v>0.4045</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7031</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3825</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3206</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3286</v>
+        <v>-0.0747</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1154</v>
+        <v>-0.4792</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2132</v>
+        <v>0.4045</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.045</v>
+        <v>0.1616</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9546</v>
+        <v>-0.0805</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.2421</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3466</v>
+        <v>-0.1767</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4789</v>
+        <v>-1.58</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1323</v>
+        <v>1.4033</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5255</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0165</v>
+        <v>0.1534</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2037</v>
+        <v>0.1026</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2202</v>
+        <v>0.0508</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2236</v>
+        <v>-1.4386</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6951</v>
+        <v>-3.0905</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4715</v>
+        <v>1.6519</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7256</v>
+        <v>-0.7915</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0336</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3079</v>
+        <v>-1.4019</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8457</v>
+        <v>-0.362</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.6145</v>
+        <v>0.9043</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7688</v>
+        <v>-1.2663</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1201</v>
+        <v>-0.4295</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.419</v>
+        <v>-0.2939</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5391</v>
+        <v>-0.1356</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2601</v>
+        <v>0.3529</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8035</v>
+        <v>-0.2123</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4566</v>
+        <v>0.5653</v>
       </c>
       <c r="V23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W23" t="n">
         <v>0.6093</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.4959</v>
-      </c>
       <c r="X23" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5955</v>
+        <v>-1.9314</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7872</v>
+        <v>-2.4029</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1916</v>
+        <v>0.4715</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7915</v>
+        <v>-1.7256</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6104000000000001</v>
+        <v>-3.0336</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4019</v>
+        <v>1.3079</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.362</v>
+        <v>-1.8457</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9043</v>
+        <v>-2.6145</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2663</v>
+        <v>0.7688</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4295</v>
+        <v>0.1201</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2939</v>
+        <v>-0.419</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1356</v>
+        <v>0.5391</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7348</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>0.196</v>
+        <v>0.5523</v>
       </c>
       <c r="T24" t="n">
-        <v>0.091</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.105</v>
+        <v>0.4566</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6093</v>
+        <v>0.6093</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6093</v>
+        <v>1.4959</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="25">
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.3218</v>
+        <v>12.67</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.7166</v>
+        <v>-8.716499999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>20.0384</v>
+        <v>21.3864</v>
       </c>
       <c r="G25" t="n">
-        <v>6.0707</v>
+        <v>6.070700000000001</v>
       </c>
       <c r="H25" t="n">
         <v>1.3481</v>
       </c>
       <c r="I25" t="n">
-        <v>4.722599999999998</v>
+        <v>4.7226</v>
       </c>
       <c r="J25" t="n">
-        <v>3.873999999999999</v>
+        <v>3.874000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>2.5172</v>
@@ -2392,7 +2392,7 @@
         <v>-1.169</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3656</v>
+        <v>3.365599999999999</v>
       </c>
       <c r="P25" t="n">
         <v>3.906899999999999</v>
@@ -2404,13 +2404,13 @@
         <v>19.5343</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9534</v>
+        <v>3.3016</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.337499999999999</v>
+        <v>-2.3372</v>
       </c>
       <c r="U25" t="n">
-        <v>4.2908</v>
+        <v>5.6389</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6093</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484327_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484327_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.1213</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,6 +1295,11 @@
       </c>
       <c r="X10" t="n">
         <v>0.0664</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-5.374000000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,11 +1541,16 @@
       <c r="X13" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9136</v>
+        <v>2.7696</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0394</v>
+        <v>-0.0218</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8743</v>
+        <v>2.7914</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0667</v>
+        <v>0.6387</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9197</v>
+        <v>0.3694</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1471</v>
+        <v>0.2692</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0908</v>
+        <v>0.3194</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2689</v>
+        <v>0.1842</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8219</v>
+        <v>0.1352</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0241</v>
+        <v>0.3193</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3492</v>
+        <v>0.1852</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0069</v>
+        <v>0.3728</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.524</v>
+        <v>-0.1924</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5309</v>
+        <v>0.5653</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1645,72 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7696</v>
+        <v>2.6066</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0218</v>
+        <v>1.7324</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7914</v>
+        <v>0.8743</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6387</v>
+        <v>1.7598</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3694</v>
+        <v>0.6127</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2692</v>
+        <v>1.1471</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3194</v>
+        <v>2.7838</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1842</v>
+        <v>0.9619</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1352</v>
+        <v>1.8219</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3193</v>
+        <v>-1.0241</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1852</v>
+        <v>-0.3492</v>
       </c>
       <c r="O15" t="n">
-        <v>0.134</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3728</v>
+        <v>0.0069</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1924</v>
+        <v>-0.524</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5653</v>
+        <v>0.5309</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,11 +2122,16 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1767</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.58</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4033</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5255</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1072</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4183</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5105</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0422</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1494</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1534</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1026</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0508</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1393</v>
+        <v>-0.1767</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7346</v>
+        <v>-1.58</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4047</v>
+        <v>1.4033</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0788</v>
+        <v>-0.5255</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.1072</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0788</v>
+        <v>-0.4183</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6741</v>
+        <v>-0.5105</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>-0.5527</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4047</v>
+        <v>-0.015</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1494</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4047</v>
+        <v>0.1344</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0605</v>
+        <v>0.1534</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0605</v>
+        <v>0.1026</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.0508</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,12 +2287,17 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>I. MACIAS MERINO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4386</v>
+        <v>-1.1393</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0905</v>
+        <v>-0.7346</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6519</v>
+        <v>-0.4047</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7915</v>
+        <v>-1.0788</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6104000000000001</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4019</v>
+        <v>-1.0788</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.362</v>
+        <v>-0.6741</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9043</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2663</v>
+        <v>-0.6741</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4295</v>
+        <v>-0.4047</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2939</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1356</v>
+        <v>-0.4047</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3529</v>
+        <v>-0.0605</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2123</v>
+        <v>-0.0605</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5653</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9314</v>
+        <v>-1.4386</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4029</v>
+        <v>-3.0905</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4715</v>
+        <v>1.6519</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7256</v>
+        <v>-0.7915</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0336</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3079</v>
+        <v>-1.4019</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8457</v>
+        <v>-0.362</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.6145</v>
+        <v>0.9043</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7688</v>
+        <v>-1.2663</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1201</v>
+        <v>-0.4295</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.419</v>
+        <v>-0.2939</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5391</v>
+        <v>-0.1356</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5523</v>
+        <v>0.3529</v>
       </c>
       <c r="T24" t="n">
-        <v>0.09569999999999999</v>
+        <v>-0.2123</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4566</v>
+        <v>0.5653</v>
       </c>
       <c r="V24" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W24" t="n">
         <v>0.6093</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.4959</v>
-      </c>
       <c r="X24" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.9314</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.4029</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.7256</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.0336</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.3079</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.8457</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.6145</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7688</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1201</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.419</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484327_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>12.67</v>
       </c>
-      <c r="E25" t="n">
-        <v>-8.716499999999998</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="E26" t="n">
+        <v>-8.7165</v>
+      </c>
+      <c r="F26" t="n">
         <v>21.3864</v>
       </c>
-      <c r="G25" t="n">
-        <v>6.070700000000001</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.3481</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="G26" t="n">
+        <v>6.070800000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.348100000000001</v>
+      </c>
+      <c r="I26" t="n">
         <v>4.7226</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>3.874000000000001</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>2.5172</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>1.3569</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>2.196499999999999</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-1.169</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>3.365599999999999</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>3.906899999999999</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-15.6275</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>19.5343</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>3.3016</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-2.3372</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>5.6389</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>-0.6093</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>5.374099999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-5.9833</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
